--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488282_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488282_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4085</v>
+        <v>7.3659</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5494</v>
+        <v>4.0391</v>
       </c>
       <c r="F2" t="n">
-        <v>2.859</v>
+        <v>3.3268</v>
       </c>
       <c r="G2" t="n">
         <v>6.9485</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8757</v>
+        <v>0.0818</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4166</v>
+        <v>0.0731</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4591</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.4474</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.076</v>
+        <v>5.2461</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4405</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6355</v>
+        <v>4.4139</v>
       </c>
       <c r="G3" t="n">
         <v>2.3535</v>
@@ -688,13 +688,13 @@
         <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2178</v>
+        <v>0.388</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3619</v>
+        <v>0.0299</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5797</v>
+        <v>0.3581</v>
       </c>
       <c r="V3" t="n">
         <v>1.7635</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.24</v>
+        <v>1.7072</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7349</v>
+        <v>3.8328</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.4949</v>
+        <v>-2.1256</v>
       </c>
       <c r="G4" t="n">
         <v>2.7828</v>
@@ -766,13 +766,13 @@
         <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3221</v>
+        <v>0.1452</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2027</v>
+        <v>0.3006</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5248</v>
+        <v>-0.1555</v>
       </c>
       <c r="V4" t="n">
         <v>0.8174</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0685</v>
+        <v>1.2392</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7701</v>
+        <v>2.0639</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7016</v>
+        <v>-0.8247</v>
       </c>
       <c r="G5" t="n">
         <v>0.7319</v>
@@ -844,13 +844,13 @@
         <v>1.8529</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6292</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0161</v>
+        <v>0.2776</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6454</v>
+        <v>0.5223</v>
       </c>
       <c r="V5" t="n">
         <v>0.8191000000000001</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ AMESTOY</t>
+          <t>Á. GONZÁLEZ PALOMO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.028</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1803</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8477</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5305</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0407</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4899</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2413</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1813</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2893</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9807</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6914</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5198</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4216</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0982</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Á. GONZÁLEZ PALOMO</t>
+          <t>A. FERNANDEZ AMESTOY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.8069</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.0824</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.7246</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9661999999999999</v>
+        <v>-0.5305</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9661999999999999</v>
+        <v>-0.0407</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.4899</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9661999999999999</v>
+        <v>-0.2413</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.1813</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.2893</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.9807</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.6914</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.2988</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.3236</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.0249</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>A. ÁLVAREZ RICO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8498</v>
+        <v>0.6441</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8692</v>
+        <v>0.6441</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0194</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1185</v>
+        <v>0.6441</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0521</v>
+        <v>0.6441</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1706</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2777</v>
+        <v>0.6441</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2362</v>
+        <v>0.6441</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1591</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2883</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1292</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3433</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8156</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4723</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ÁLVAREZ RICO</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6441</v>
+        <v>0.2538</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6441</v>
+        <v>-0.8144</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.0683</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6441</v>
+        <v>1.7699</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6441</v>
+        <v>1.5424</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.2275</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6441</v>
+        <v>1.7286</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6441</v>
+        <v>2.8684</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.1398</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.0413</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.326</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.3673</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.5956</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.2363</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.3594</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3473</v>
+        <v>0.2535</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2173</v>
+        <v>0.1689</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.87</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4521</v>
+        <v>-0.0835</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3325</v>
+        <v>0.6888</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1196</v>
+        <v>-0.7724</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2187</v>
+        <v>1.0117</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2187</v>
+        <v>0.9702</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6708</v>
+        <v>-1.0952</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5513</v>
+        <v>-0.2814</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1196</v>
+        <v>-0.8138</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1853</v>
+        <v>-1.1117</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5579</v>
+        <v>0.6482</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1839</v>
+        <v>0.2689</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3741</v>
+        <v>0.3793</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3144</v>
+        <v>-0.1259</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3144</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3031</v>
+        <v>0.0434</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8144</v>
+        <v>-0.208</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1175</v>
+        <v>0.2514</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7699</v>
+        <v>0.1185</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5424</v>
+        <v>-1.0521</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2275</v>
+        <v>1.1706</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7286</v>
+        <v>0.2777</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8684</v>
+        <v>0.2362</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1398</v>
+        <v>0.0415</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0413</v>
+        <v>-0.1591</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.326</v>
+        <v>-1.2883</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3673</v>
+        <v>1.1292</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4823</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6449</v>
+        <v>0.5369</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2363</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4086</v>
+        <v>-0.2015</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6294</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3089</v>
+        <v>-0.66</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5165999999999999</v>
+        <v>0.8256</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2077</v>
+        <v>-1.4856</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0835</v>
+        <v>-2.4521</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6888</v>
+        <v>-0.3325</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7724</v>
+        <v>-2.1196</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0117</v>
+        <v>0.2187</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9702</v>
+        <v>0.2187</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0952</v>
+        <v>-2.6708</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2814</v>
+        <v>-0.5513</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8138</v>
+        <v>-2.1196</v>
       </c>
       <c r="P12" t="n">
+        <v>0.5558999999999999</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-0.1853</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-1.1117</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0858</v>
+        <v>1.5507</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4166</v>
+        <v>0.7921</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5024</v>
+        <v>0.7585</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1259</v>
+        <v>-0.3144</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1259</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1135</v>
+        <v>-3.3575</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8883</v>
+        <v>-1.28</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2252</v>
+        <v>-2.0775</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4472</v>
@@ -1468,13 +1468,13 @@
         <v>0.3706</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2612</v>
+        <v>1.0172</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2933</v>
+        <v>0.9016</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0321</v>
+        <v>0.1156</v>
       </c>
       <c r="V13" t="n">
         <v>-1.26</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.5091</v>
+        <v>14.5088</v>
       </c>
       <c r="E14" t="n">
-        <v>11.1527</v>
+        <v>11.1528</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3563</v>
+        <v>3.3562</v>
       </c>
       <c r="G14" t="n">
         <v>11.8021</v>
@@ -1531,7 +1531,7 @@
         <v>-9.533899999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.616300000000001</v>
+        <v>-7.6163</v>
       </c>
       <c r="O14" t="n">
         <v>-1.917700000000001</v>
@@ -1546,16 +1546,16 @@
         <v>12.9701</v>
       </c>
       <c r="S14" t="n">
-        <v>6.062099999999999</v>
+        <v>6.0623</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9422</v>
+        <v>3.9421</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1201</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>2.203200000000001</v>
+        <v>2.2032</v>
       </c>
       <c r="W14" t="n">
         <v>4.4032</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1378</v>
+        <v>5.6224</v>
       </c>
       <c r="E15" t="n">
-        <v>8.958600000000001</v>
+        <v>8.273099999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8208</v>
+        <v>-2.6507</v>
       </c>
       <c r="G15" t="n">
         <v>5.6466</v>
@@ -1624,13 +1624,13 @@
         <v>3.7057</v>
       </c>
       <c r="S15" t="n">
-        <v>0.101</v>
+        <v>-0.4144</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5783</v>
+        <v>-0.1072</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4773</v>
+        <v>-0.3072</v>
       </c>
       <c r="V15" t="n">
         <v>-2.2038</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5455</v>
+        <v>1.0362</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8862</v>
+        <v>2.7883</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3408</v>
+        <v>-1.7521</v>
       </c>
       <c r="G16" t="n">
         <v>0.8982</v>
@@ -1702,13 +1702,13 @@
         <v>3.5205</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2241</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0746</v>
+        <v>-0.1725</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1495</v>
+        <v>-0.5609</v>
       </c>
       <c r="V16" t="n">
         <v>0.3155</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1439</v>
+        <v>0.9846</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1521</v>
+        <v>0.5334</v>
       </c>
       <c r="F17" t="n">
-        <v>0.296</v>
+        <v>0.4512</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4151</v>
@@ -1780,13 +1780,13 @@
         <v>3.3352</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.053</v>
+        <v>-0.2123</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.1476</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2199</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0.315</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5312</v>
+        <v>-2.155</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5244</v>
+        <v>-0.4265</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0068</v>
+        <v>-1.7285</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1723</v>
@@ -1858,13 +1858,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9709</v>
+        <v>-0.5947</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5471</v>
+        <v>-0.4492</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4238</v>
+        <v>-0.1455</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9439</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7208</v>
+        <v>-3.2924</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8429</v>
+        <v>-3.6264</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1221</v>
+        <v>0.334</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7176</v>
@@ -1936,13 +1936,13 @@
         <v>3.5205</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6835</v>
+        <v>0.1119</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0707</v>
+        <v>0.2873</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3873</v>
+        <v>-0.1754</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3161</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8287</v>
+        <v>-3.4456</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9905</v>
+        <v>-1.7946</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8382</v>
+        <v>-1.6509</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2199</v>
@@ -2014,13 +2014,13 @@
         <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3674</v>
+        <v>-0.9843</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8207</v>
+        <v>-0.6249</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5467</v>
+        <v>-0.3594</v>
       </c>
       <c r="V20" t="n">
         <v>0.3144</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7178</v>
+        <v>-4.4652</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7628</v>
+        <v>-2.567</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9549</v>
+        <v>-1.8982</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8507</v>
@@ -2092,13 +2092,13 @@
         <v>0.1853</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8115</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6566</v>
+        <v>-0.4607</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.155</v>
+        <v>-0.0982</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3144</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.5376</v>
+        <v>-6.8355</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.9282</v>
+        <v>-6.5364</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.299</v>
       </c>
       <c r="G22" t="n">
         <v>-8.971399999999999</v>
@@ -2170,13 +2170,13 @@
         <v>3.3352</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4196</v>
+        <v>-0.7175</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8369</v>
+        <v>-0.4452</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5827</v>
+        <v>-0.2724</v>
       </c>
       <c r="V22" t="n">
         <v>0.63</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-14.5089</v>
+        <v>-12.5505</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3561</v>
+        <v>-3.356100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.1528</v>
+        <v>-9.194199999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-11.8022</v>
@@ -2248,13 +2248,13 @@
         <v>18.5289</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.061999999999999</v>
+        <v>-4.1037</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.1201</v>
+        <v>-2.12</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.9422</v>
+        <v>-1.9837</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2033</v>
